--- a/multiSchoolOutput/03_School_of_Economics/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/03_School_of_Economics/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -752,7 +752,7 @@
         <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -870,7 +870,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -988,7 +988,7 @@
         <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1047,7 +1047,7 @@
         <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1106,7 +1106,7 @@
         <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1283,7 +1283,7 @@
         <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1401,7 +1401,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1519,7 +1519,7 @@
         <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2651,12 +2651,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4315,7 +4315,7 @@
         <v>80</v>
       </c>
       <c r="F65" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5291,7 +5291,7 @@
         <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5901,7 +5901,7 @@
         <v>120</v>
       </c>
       <c r="F91" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6450,7 +6450,7 @@
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6511,7 +6511,7 @@
         <v>80</v>
       </c>
       <c r="F101" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6555,12 +6555,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6633,7 +6633,7 @@
         <v>80</v>
       </c>
       <c r="F103" t="n">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6677,12 +6677,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0228_-1_LG.07</t>
+          <t>0209_-1_B.Z28</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0227_00_G.04</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7731,7 +7731,7 @@
         <v>100</v>
       </c>
       <c r="F121" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0422_J_J.03</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9056,12 +9056,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10154,12 +10154,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0229_01_1.A</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10232,7 +10232,7 @@
         <v>420</v>
       </c>
       <c r="F162" t="n">
-        <v>458</v>
+        <v>350</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -10276,12 +10276,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10293,7 +10293,7 @@
         <v>91</v>
       </c>
       <c r="F163" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -10337,12 +10337,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10354,7 +10354,7 @@
         <v>30</v>
       </c>
       <c r="F164" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10459,12 +10459,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10476,7 +10476,7 @@
         <v>30</v>
       </c>
       <c r="F166" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10703,12 +10703,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10947,12 +10947,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10964,7 +10964,7 @@
         <v>80</v>
       </c>
       <c r="F174" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11374,12 +11374,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0227_01_1.06</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0311_02_2.02</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11984,12 +11984,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0225_02_2.201</t>
+          <t>0229_01_1.A</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12184,7 +12184,7 @@
         <v>400</v>
       </c>
       <c r="F194" t="n">
-        <v>458</v>
+        <v>350</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0001_00_G.159</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12306,7 +12306,7 @@
         <v>80</v>
       </c>
       <c r="F196" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0311_02_2.02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">

--- a/multiSchoolOutput/03_School_of_Economics/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/03_School_of_Economics/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -752,7 +752,7 @@
         <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -870,7 +870,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -912,12 +912,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -988,7 +988,7 @@
         <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1047,7 +1047,7 @@
         <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1106,7 +1106,7 @@
         <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1283,7 +1283,7 @@
         <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1401,7 +1401,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1519,7 +1519,7 @@
         <v>80</v>
       </c>
       <c r="F19" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0335_03_3.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4315,7 +4315,7 @@
         <v>80</v>
       </c>
       <c r="F65" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5291,7 +5291,7 @@
         <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0335_02_2.1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5901,7 +5901,7 @@
         <v>120</v>
       </c>
       <c r="F91" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0209_-1_B.Z28</t>
+          <t>0008_03_3.454</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6450,7 +6450,7 @@
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6511,7 +6511,7 @@
         <v>80</v>
       </c>
       <c r="F101" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6633,7 +6633,7 @@
         <v>80</v>
       </c>
       <c r="F103" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6677,12 +6677,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0001_01_1.265</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7731,7 +7731,7 @@
         <v>100</v>
       </c>
       <c r="F121" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0228_04_4.18</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0103_03_3.D02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.274</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -9056,12 +9056,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0001_01_1.273</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9605,12 +9605,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0229_01_1.A</t>
+          <t>0225_02_2.201</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10232,7 +10232,7 @@
         <v>420</v>
       </c>
       <c r="F162" t="n">
-        <v>350</v>
+        <v>458</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -10276,12 +10276,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10293,7 +10293,7 @@
         <v>91</v>
       </c>
       <c r="F163" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -10337,12 +10337,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0335_04_4.2</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10354,7 +10354,7 @@
         <v>30</v>
       </c>
       <c r="F164" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -10398,12 +10398,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10459,12 +10459,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0335_01_1.9</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10476,7 +10476,7 @@
         <v>30</v>
       </c>
       <c r="F166" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -10520,12 +10520,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.276</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.265</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10964,7 +10964,7 @@
         <v>80</v>
       </c>
       <c r="F174" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11374,12 +11374,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0335_04_4.3</t>
+          <t>0227_01_1.06</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11618,12 +11618,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0311_02_2.01</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0008_03_3.454</t>
+          <t>0335_04_4.3</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11923,12 +11923,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0001_01_1.274</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11984,12 +11984,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_01_1.1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0001_01_1.276</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0229_01_1.A</t>
+          <t>0225_02_2.201</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12184,7 +12184,7 @@
         <v>400</v>
       </c>
       <c r="F194" t="n">
-        <v>350</v>
+        <v>458</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0001_00_G.159</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12306,7 +12306,7 @@
         <v>80</v>
       </c>
       <c r="F196" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0311_02_2.01</t>
+          <t>0001_01_1.273</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
